--- a/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:30</t>
+          <t>2026-09-09 00:50:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:32</t>
+          <t>2026-09-09 00:50:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:33</t>
+          <t>2026-09-09 00:50:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:34</t>
+          <t>2026-09-09 00:50:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:41</t>
+          <t>2026-09-09 01:16:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:42</t>
+          <t>2026-09-09 01:16:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:44</t>
+          <t>2026-09-09 01:16:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:45</t>
+          <t>2026-09-09 01:16:12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.70%1,794,000</t>
+          <t>8.62%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.70%</t>
+          <t>8.62%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.81%736,000</t>
+          <t>6.64%736,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>6.64%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>+1.08%750</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2340</v>
+        <v>750</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.39%1,391,225</t>
+          <t>5.48%3,745,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.39%</t>
+          <t>5.48%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1391225</v>
+        <v>3745000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.41%742</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>742</v>
+        <v>2325</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.46%3,745,000</t>
+          <t>5.31%1,171,225</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.31%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3745000</v>
+        <v>1171225</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2%441.5</t>
+          <t>+5.1%464</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>+5.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>441.5</v>
+        <v>464</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.95%5,709,000</t>
+          <t>5.16%5,709,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.16%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.45%181,000</t>
+          <t>4.38%181,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2265</v>
+        <v>2335</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.66%824,000</t>
+          <t>3.75%824,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,34 +931,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5795</v>
+        <v>6870</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.49%307,000</t>
+          <t>3.39%253,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>307000</v>
+        <v>253000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.32%1490</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1490</v>
+        <v>5615</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.45%1,180,000</t>
+          <t>3.36%307,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1180000</v>
+        <v>307000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>-2.35%1455</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5340</v>
+        <v>1455</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.28%313,000</t>
+          <t>3.35%1,180,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>313000</v>
+        <v>1180000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6500</v>
+        <v>5375</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.23%253,000</t>
+          <t>3.28%313,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>253000</v>
+        <v>313000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.8%505</t>
+          <t>+7.3%999</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>505</v>
+        <v>999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.13%3,158,000</t>
+          <t>3.23%1,660,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3158000</v>
+        <v>1660000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.02%931</t>
+          <t>-0.59%502</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>931</v>
+        <v>502</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.03%1,660,000</t>
+          <t>3.09%3,158,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1660000</v>
+        <v>3158000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3285</v>
+        <v>3380</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.40%372,000</t>
+          <t>2.45%372,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:08</t>
+          <t>2026-09-09 19:33:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1955</v>
+        <v>2015</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.38%621,000</t>
+          <t>2.44%621,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.65%955</t>
+          <t>0%955</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.05%1,096,000</t>
+          <t>2.04%1,096,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.38%657</t>
+          <t>-0.61%653</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.88%1,460,000</t>
+          <t>1.86%1,460,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.68%291</t>
+          <t>+0.52%292.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>291</v>
+        <v>292.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3%515</t>
+          <t>+3.5%533</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.56%1,545,000</t>
+          <t>1.61%1,545,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.49%740</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>740</v>
+        <v>141.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.44%990,000</t>
+          <t>1.43%5,174,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>990000</v>
+        <v>5174000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>-1.35%730</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>137</v>
+        <v>730</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.39%5,174,000</t>
+          <t>1.41%990,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>5174000</v>
+        <v>990000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>+1.34%189</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>19220</v>
+        <v>189</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.35%35,900</t>
+          <t>1.36%3,682,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>35900</v>
+        <v>3682000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.33%186.5</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>186.5</v>
+        <v>18605</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.35%3,682,000</t>
+          <t>1.30%35,900</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3682000</v>
+        <v>35900</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.79%152.5</t>
+          <t>+1.35%187.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>152.5</v>
+        <v>187.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.29%4,294,000</t>
+          <t>1.27%3,482,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4294000</v>
+        <v>3482000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%185</t>
+          <t>+0.56%181</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.26%3,482,000</t>
+          <t>1.22%3,459,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3482000</v>
+        <v>3459000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.06%357</t>
+          <t>-2.1%349.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>357</v>
+        <v>349.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.23%1,761,000</t>
+          <t>1.20%1,761,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.91%180</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.91%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>180</v>
+        <v>640</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.22%3,459,000</t>
+          <t>1.17%936,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3459000</v>
+        <v>936000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.45%610</t>
+          <t>-4.75%581</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>610</v>
+        <v>581</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.20%1,000,000</t>
+          <t>1.13%1,000,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.31%253.5</t>
+          <t>+0.45%90</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>253.5</v>
+        <v>90</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.15%2,302,000</t>
+          <t>1.13%6,424,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2302000</v>
+        <v>6424000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:09</t>
+          <t>2026-09-09 19:33:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>-1.97%248.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>618</v>
+        <v>248.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.14%936,000</t>
+          <t>1.12%2,302,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>936000</v>
+        <v>2302000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.03%89.6</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>89.59999999999999</v>
+        <v>1345</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.13%6,424,000</t>
+          <t>1.11%424,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>6424000</v>
+        <v>424000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>+0.6%167.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1345</v>
+        <v>167.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.12%424,000</t>
+          <t>1.11%3,393,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>424000</v>
+        <v>3393000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.4%166.5</t>
+          <t>-0.9%166</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>166.5</v>
+        <v>166</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.11%3,393,000</t>
+          <t>1.08%3,324,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>3393000</v>
+        <v>3324000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.33%167.5</t>
+          <t>+1.24%122.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+1.24%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>167.5</v>
+        <v>122.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.09%3,324,000</t>
+          <t>1.05%4,389,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>3324000</v>
+        <v>4389000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.72%121</t>
+          <t>+2%281</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.72%</t>
+          <t>+2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>121</v>
+        <v>281</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.04%4,389,000</t>
+          <t>1.05%1,910,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>4389000</v>
+        <v>1910000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.61%275.5</t>
+          <t>+2.62%156.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>275.5</v>
+        <v>156.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.03%1,910,000</t>
+          <t>1.04%3,400,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1910000</v>
+        <v>3400000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1225</v>
+        <v>1345</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.92%382,000</t>
+          <t>1.00%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.84%412.5</t>
+          <t>-1.21%407.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>412.5</v>
+        <v>407.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.84%1,032,000</t>
+          <t>0.82%1,032,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.54%245.5</t>
+          <t>+1.63%249.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.54%</t>
+          <t>+1.63%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>245.5</v>
+        <v>249.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.77%1,607,000</t>
+          <t>0.78%1,607,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.63%851</t>
+          <t>+1.29%862</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>+1.29%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+9.92%2825</t>
+          <t>-1.59%2780</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2825</v>
+        <v>2780</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.52%93,000</t>
+          <t>0.50%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.84%294</t>
+          <t>+6.16%534</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>294</v>
+        <v>534</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.31%533,000</t>
+          <t>0.32%304,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>533000</v>
+        <v>304000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.57%70.6</t>
+          <t>+1.87%299.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>70.59999999999999</v>
+        <v>299.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.31%2,213,556</t>
+          <t>0.31%533,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2213556</v>
+        <v>533000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.05%119.5</t>
+          <t>-1.27%69.7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.05%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>119.5</v>
+        <v>69.7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.30%1,281,000</t>
+          <t>0.30%2,213,556</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1281000</v>
+        <v>2213556</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:11</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.14%503</t>
+          <t>+0.42%120</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>503</v>
+        <v>120</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.30%304,000</t>
+          <t>0.30%1,281,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>304000</v>
+        <v>1281000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>8070長華*</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.41%245</t>
+          <t>-0.3%49.85</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>245</v>
+        <v>49.85</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.28%577,000</t>
+          <t>0.27%2,792,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>577000</v>
+        <v>2792000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-6.54%1215</t>
+          <t>-1.23%1200</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-6.54%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1215</v>
+        <v>1200</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.28%116,000</t>
+          <t>0.27%116,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,25 +3371,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8070長華*</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.2%50</t>
+          <t>-1.63%241</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>50</v>
+        <v>241</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.27%2,792,000</t>
+          <t>0.27%577,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3398,11 +3398,11 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2792000</v>
+        <v>577000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+6.04%1405</t>
+          <t>-4.27%1345</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1405</v>
+        <v>1345</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.12%42,000</t>
+          <t>0.11%42,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.74%47.75</t>
+          <t>+1.47%48.45</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>47.75</v>
+        <v>48.45</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5960</v>
+        <v>5925</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+0.29%175</t>
+          <t>-0.57%174</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>+0.97%520</t>
+          <t>+1.15%526</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-1.49%728</t>
+          <t>+0.96%735</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3798,25 +3798,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>2886兆豐金</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-0.33%149</t>
+          <t>-0.59%50.3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>149</v>
+        <v>50.3</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0%250</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:12</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3859,25 +3859,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2886兆豐金</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+0.8%50.6</t>
+          <t>-1.34%147</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>50.6</v>
+        <v>147</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0%250</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:18</t>
+          <t>2026-09-09 22:36:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:19</t>
+          <t>2026-09-09 22:36:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-09 22:36:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-09 22:36:47</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:43</t>
+          <t>2026-09-09 22:47:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:44</t>
+          <t>2026-09-09 22:47:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:45</t>
+          <t>2026-09-09 22:47:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:47</t>
+          <t>2026-09-09 22:47:52</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:48</t>
+          <t>2026-09-09 23:09:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:49</t>
+          <t>2026-09-09 23:09:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:50</t>
+          <t>2026-09-09 23:09:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:52</t>
+          <t>2026-09-09 23:09:46</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
